--- a/artfynd/A 14048-2026 artfynd.xlsx
+++ b/artfynd/A 14048-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132020906</v>
       </c>
       <c r="B2" t="n">
-        <v>57903</v>
+        <v>57904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>132021057</v>
       </c>
       <c r="B3" t="n">
-        <v>96276</v>
+        <v>96277</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14048-2026 artfynd.xlsx
+++ b/artfynd/A 14048-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132020906</v>
       </c>
       <c r="B2" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>132021057</v>
       </c>
       <c r="B3" t="n">
-        <v>96277</v>
+        <v>96282</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14048-2026 artfynd.xlsx
+++ b/artfynd/A 14048-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132020906</v>
       </c>
       <c r="B2" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>132021057</v>
       </c>
       <c r="B3" t="n">
-        <v>96282</v>
+        <v>96284</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14048-2026 artfynd.xlsx
+++ b/artfynd/A 14048-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>132021057</v>
       </c>
       <c r="B3" t="n">
-        <v>96325</v>
+        <v>96328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14048-2026 artfynd.xlsx
+++ b/artfynd/A 14048-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132020906</v>
       </c>
       <c r="B2" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>132021057</v>
       </c>
       <c r="B3" t="n">
-        <v>96328</v>
+        <v>96336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14048-2026 artfynd.xlsx
+++ b/artfynd/A 14048-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132020906</v>
       </c>
       <c r="B2" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>132021057</v>
       </c>
       <c r="B3" t="n">
-        <v>96336</v>
+        <v>96346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14048-2026 artfynd.xlsx
+++ b/artfynd/A 14048-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>132021057</v>
       </c>
       <c r="B3" t="n">
-        <v>96346</v>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14048-2026 artfynd.xlsx
+++ b/artfynd/A 14048-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -892,6 +892,128 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133065041</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97789</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2606</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Klippfrullania</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Glömsten, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>342291</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6432022</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mycket, på flera klena rönnar.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>vanlig rönn</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia subsp. aucuparia</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia subsp. aucuparia</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14048-2026 artfynd.xlsx
+++ b/artfynd/A 14048-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>133065041</v>
       </c>
       <c r="B4" t="n">
-        <v>97789</v>
+        <v>97792</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 14048-2026 artfynd.xlsx
+++ b/artfynd/A 14048-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>133065041</v>
       </c>
       <c r="B4" t="n">
-        <v>97792</v>
+        <v>97793</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 14048-2026 artfynd.xlsx
+++ b/artfynd/A 14048-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>133065041</v>
       </c>
       <c r="B4" t="n">
-        <v>97793</v>
+        <v>97797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 14048-2026 artfynd.xlsx
+++ b/artfynd/A 14048-2026 artfynd.xlsx
@@ -675,48 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132020906</v>
+        <v>133065041</v>
       </c>
       <c r="B2" t="n">
-        <v>57950</v>
+        <v>97862</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Glömsten, Glömsten, Vg</t>
+          <t>Glömsten, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>342253</v>
+        <v>342291</v>
       </c>
       <c r="R2" t="n">
-        <v>6432033</v>
+        <v>6432022</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,27 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:10</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:10</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ganska färska spår av födosök på låga.</t>
+          <t>Mycket, på flera klena rönnar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,18 +763,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>vanlig rönn</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia subsp. aucuparia</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia subsp. aucuparia</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -790,7 +800,7 @@
         <v>132021057</v>
       </c>
       <c r="B3" t="n">
-        <v>96348</v>
+        <v>96423</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133065041</v>
+        <v>132020906</v>
       </c>
       <c r="B4" t="n">
-        <v>97807</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,41 +915,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Glömsten, Vg</t>
+          <t>Glömsten, Glömsten, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>342291</v>
+        <v>342253</v>
       </c>
       <c r="R4" t="n">
-        <v>6432022</v>
+        <v>6432033</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,17 +969,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Mycket, på flera klena rönnar.</t>
+          <t>Ganska färska spår av födosök på låga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -982,34 +998,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>vanlig rönn</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia subsp. aucuparia</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia subsp. aucuparia</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 14048-2026 artfynd.xlsx
+++ b/artfynd/A 14048-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133065041</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132021057</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,8 +1028,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132020906</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>